--- a/sample_files/sample_invalid.xlsx
+++ b/sample_files/sample_invalid.xlsx
@@ -435,16 +435,16 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Order_No</t>
+          <t>Order_no</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -469,22 +469,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>No_of_Batches</t>
+          <t>Number_of_Batches</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Waybill_No</t>
+          <t>Waybill_Number</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Batch_No</t>
+          <t>Batch_Number</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Bag_No</t>
+          <t>BagNumber</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -530,7 +530,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
